--- a/AAII_Financials/Yearly/PBFS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PBFS_YR_FIN.xlsx
@@ -2841,7 +2841,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>50600</v>
+        <v>58000</v>
       </c>
       <c r="E58" s="3">
         <v>53700</v>
@@ -2937,7 +2937,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1789800</v>
+        <v>1797100</v>
       </c>
       <c r="E60" s="3">
         <v>1639900</v>
@@ -3033,7 +3033,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>32200</v>
+        <v>24800</v>
       </c>
       <c r="E62" s="3">
         <v>28800</v>
